--- a/data/output/Garches_Equipe_1_feuille.xlsx
+++ b/data/output/Garches_Equipe_1_feuille.xlsx
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -528,7 +528,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>

--- a/data/output/Garches_Equipe_1_feuille.xlsx
+++ b/data/output/Garches_Equipe_1_feuille.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ville/Commune</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>equipe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nb_traversees</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>coordonnees</t>
         </is>
@@ -483,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,23 +480,20 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>48.838467608,2.171797485</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>48.839372363,2.171812121</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,16 +507,13 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>48.839372363,2.171812121</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>48.838467608,2.171797485</t>
         </is>
       </c>
     </row>
@@ -557,14 +534,11 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>48.838040862,2.169032756</t>
         </is>
@@ -587,14 +561,11 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>48.837882396,2.168128382</t>
         </is>

--- a/data/output/Garches_Equipe_1_feuille.xlsx
+++ b/data/output/Garches_Equipe_1_feuille.xlsx
@@ -413,25 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coordonnees</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ville/Commune</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>equipe</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
@@ -439,137 +439,204 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>traversee</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>coordonnees</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>48.838467608,2.171797485</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>48.839372363,2.171812121</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>48.838467608,2.171797485</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>48.838467608,2.171797485</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>48.838040862,2.169032756</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
+          <t>48.838467608,2.171797485</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>48.839372363,2.171812121</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48.838040862,2.169032756</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>48.837882396,2.168128382</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/output/Garches_Equipe_1_feuille.xlsx
+++ b/data/output/Garches_Equipe_1_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.839372363,2.171812121</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,12 +594,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.842956926,2.186487926</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -619,25 +619,625 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.842956926,2.186487926</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48.845207116,2.184629247</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48.845382622,2.183603112</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48.845382622,2.183603112</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48.844292567,2.183697322</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48.843732399,2.183521369</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rue   du  Regard  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>48.843335056,2.188106937</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48.843335056,2.188106937</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>48.843335056,2.188106937</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_1_feuille.xlsx
+++ b/data/output/Garches_Equipe_1_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.842130147,2.187364881</t>
+          <t>48.844591533,2.186878445</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.842130147,2.187364881</t>
+          <t>48.844591533,2.186878445</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.842677932,2.186438811</t>
+          <t>48.844591533,2.186878445</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.842677932,2.186438811</t>
+          <t>48.84484698,2.186514003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.842677932,2.186438811</t>
+          <t>48.84484698,2.186514003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.842956926,2.186487926</t>
+          <t>48.84484698,2.186514003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.842956926,2.186487926</t>
+          <t>48.84484698,2.186514003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.842956926,2.186487926</t>
+          <t>48.843635567,2.186699047</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.842956926,2.186487926</t>
+          <t>48.843635567,2.186699047</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.843635567,2.186699047</t>
+          <t>48.842956926,2.186487926</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.843635567,2.186699047</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.843635567,2.186699047</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.844591533,2.186878445</t>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,19 +819,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.844591533,2.186878445</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -844,19 +844,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.84484698,2.186514003</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -869,19 +869,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.84484698,2.186514003</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -894,19 +894,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.845207116,2.184629247</t>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -919,16 +919,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.845382622,2.183603112</t>
+          <t>48.843335056,2.188106937</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -944,16 +944,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>48.845382622,2.183603112</t>
+          <t>48.843335056,2.188106937</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -969,19 +969,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48.844292567,2.183697322</t>
+          <t>48.843335056,2.188106937</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -994,16 +994,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>48.843732399,2.183521369</t>
+          <t>48.844046988,2.18906415</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rue   du  Regard  /  Avenue  des  Coteaux</t>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -1019,19 +1019,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>48.845861542,2.185216473</t>
+          <t>48.844046988,2.18906415</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>48.845861542,2.185216473</t>
+          <t>48.844046988,2.18906415</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1094,19 +1094,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>48.845861542,2.185216473</t>
+          <t>48.845207116,2.184629247</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1119,19 +1119,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>48.844046988,2.18906415</t>
+          <t>48.845207116,2.184629247</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1144,19 +1144,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48.844046988,2.18906415</t>
+          <t>48.845207116,2.184629247</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1169,19 +1169,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>48.843335056,2.188106937</t>
+          <t>48.845207116,2.184629247</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+          <t>Avenue  de  Beauval  /  Avenue  des  Coteaux / Avenue  des  Coteaux  /  Avenue  de  Beauval</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>48.843335056,2.188106937</t>
+          <t>48.845382622,2.183603112</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1219,25 +1219,600 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48.843335056,2.188106937</t>
+          <t>48.845382622,2.183603112</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48.845382622,2.183603112</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>48.845382622,2.183603112</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Beauval  /  Rue  de  L'Ermitage / Avenue  de  Beauval  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>48.844292567,2.183697322</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>48.844292567,2.183697322</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>48.844292567,2.183697322</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>48.844292567,2.183697322</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  des  Coteaux  /  Impasse  du  Regard / Avenue  des  Coteaux  /  Sente  de  la  Plaine </t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>48.843732399,2.183521369</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rue   du  Regard  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>48.843732399,2.183521369</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rue   du  Regard  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>48.843732399,2.183521369</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rue   du  Regard  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>48.840938427,2.185932618</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rue  Civiale  /  Avenue  Foch</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48.840938427,2.185932618</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rue  Civiale  /  Avenue  Foch</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48.839978629,2.185739669</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>48.839978629,2.185739669</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>16</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>17</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>17</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>17</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>18</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>48.838378036,2.185179691</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>19</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
